--- a/config/PCS_英博_大机.xlsx
+++ b/config/PCS_英博_大机.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332"/>
+    <workbookView windowWidth="18519" windowHeight="11218"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>

--- a/config/PCS_英博_大机.xlsx
+++ b/config/PCS_英博_大机.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18519" windowHeight="11218"/>
+    <workbookView windowWidth="18569" windowHeight="11268" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
@@ -5451,7 +5451,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5.4957264957265" style="4" customWidth="1"/>
@@ -7022,7 +7022,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" s="3" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/config/PCS_英博_大机.xlsx
+++ b/config/PCS_英博_大机.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268" activeTab="1"/>
+    <workbookView windowWidth="22010" windowHeight="12332"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
